--- a/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
+++ b/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>剔除的起始日期后新开店总数</v>
       </c>
       <c r="B4">
-        <v>510</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B6">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>遗留店铺累计回款总额</v>
       </c>
       <c r="B7">
-        <v>77768.40000000002</v>
+        <v>79453.60000000003</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>遗留店铺累计抽点店铺次数</v>
       </c>
       <c r="B8">
-        <v>8891</v>
+        <v>9070</v>
       </c>
     </row>
     <row r="9">
@@ -475,7 +475,7 @@
         <v>导出时间</v>
       </c>
       <c r="B9" t="str">
-        <v>2026/4/12 09:36:52</v>
+        <v>2026/4/13 09:16:27</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1703,7 +1703,7 @@
         <v>167</v>
       </c>
       <c r="E42">
-        <v>1467.68</v>
+        <v>1474.61</v>
       </c>
       <c r="F42">
         <v>120</v>
@@ -1715,7 +1715,7 @@
         <v>47</v>
       </c>
       <c r="I42">
-        <v>507.99</v>
+        <v>514.92</v>
       </c>
     </row>
     <row r="43">
@@ -1729,27 +1729,56 @@
         <v>2578</v>
       </c>
       <c r="D43">
-        <v>59</v>
+        <v>189</v>
       </c>
       <c r="E43">
-        <v>428.82</v>
+        <v>1752.77</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1188.54</v>
       </c>
       <c r="H43">
         <v>59</v>
       </c>
       <c r="I43">
-        <v>428.82</v>
+        <v>564.23</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B44">
+        <v>527</v>
+      </c>
+      <c r="C44">
+        <v>2578</v>
+      </c>
+      <c r="D44">
+        <v>49</v>
+      </c>
+      <c r="E44">
+        <v>354.32</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>49</v>
+      </c>
+      <c r="I44">
+        <v>354.32</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I44"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15748,7 +15777,7 @@
         <v>王郡江</v>
       </c>
       <c r="G608" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="609">
@@ -25799,7 +25828,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1045" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1046">
@@ -26489,7 +26518,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1075" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1076">
@@ -33435,7 +33464,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1377" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1378">
@@ -34815,7 +34844,7 @@
         <v>王清月</v>
       </c>
       <c r="G1437" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1438">
@@ -40243,7 +40272,7 @@
         <v>王清月</v>
       </c>
       <c r="G1673" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1674">
@@ -42382,7 +42411,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1766" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1767">
@@ -44153,7 +44182,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1843" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1844">
@@ -45441,7 +45470,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1899" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1900">
@@ -50064,7 +50093,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2100" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2101">
@@ -52157,7 +52186,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2191" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2192">
@@ -55308,7 +55337,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2328" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2329">
@@ -55906,7 +55935,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2354" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2355">
@@ -56504,7 +56533,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2380" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2381">
@@ -59126,7 +59155,7 @@
         <v>王涛</v>
       </c>
       <c r="G2494" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2495">
@@ -59379,7 +59408,7 @@
         <v>王涛</v>
       </c>
       <c r="G2505" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2506">
@@ -59770,7 +59799,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2522" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2523">
@@ -60460,7 +60489,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2552" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2553">
@@ -61120,7 +61149,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>默认延长到最新抽点业务日期 2026-04-11。</v>
+        <v>默认延长到最新抽点业务日期 2026-04-12。</v>
       </c>
     </row>
     <row r="4">

--- a/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
+++ b/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>剔除的起始日期后新开店总数</v>
       </c>
       <c r="B4">
-        <v>527</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B6">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>遗留店铺累计回款总额</v>
       </c>
       <c r="B7">
-        <v>79453.60000000003</v>
+        <v>81115.47000000002</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>遗留店铺累计抽点店铺次数</v>
       </c>
       <c r="B8">
-        <v>9070</v>
+        <v>9245</v>
       </c>
     </row>
     <row r="9">
@@ -475,7 +475,7 @@
         <v>导出时间</v>
       </c>
       <c r="B9" t="str">
-        <v>2026/4/13 09:16:27</v>
+        <v>2026/4/14 09:35:14</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1758,27 +1758,56 @@
         <v>2578</v>
       </c>
       <c r="D44">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="E44">
-        <v>354.32</v>
+        <v>1699.76</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1190.51</v>
       </c>
       <c r="H44">
         <v>49</v>
       </c>
       <c r="I44">
-        <v>354.32</v>
+        <v>509.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B45">
+        <v>538</v>
+      </c>
+      <c r="C45">
+        <v>2578</v>
+      </c>
+      <c r="D45">
+        <v>50</v>
+      </c>
+      <c r="E45">
+        <v>316.43</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>50</v>
+      </c>
+      <c r="I45">
+        <v>316.43</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -23045,7 +23074,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G924" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="925">
@@ -29255,7 +29284,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1194" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1195">
@@ -29531,7 +29560,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1206" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1207">
@@ -38662,7 +38691,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1603" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1604">
@@ -40272,7 +40301,7 @@
         <v>王清月</v>
       </c>
       <c r="G1673" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1674">
@@ -41721,7 +41750,7 @@
         <v>王涛</v>
       </c>
       <c r="G1736" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1737">
@@ -45838,7 +45867,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1915" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1916">
@@ -47609,7 +47638,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1992" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1993">
@@ -50093,7 +50122,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2100" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2101">
@@ -50737,7 +50766,7 @@
         <v>王清月</v>
       </c>
       <c r="G2128" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2129">
@@ -55222,7 +55251,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2323" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2324">
@@ -56280,7 +56309,7 @@
         <v>王涛</v>
       </c>
       <c r="G2369" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2370">
@@ -60949,7 +60978,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2572" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2573">
@@ -61087,7 +61116,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2578" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2579">
@@ -61149,7 +61178,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>默认延长到最新抽点业务日期 2026-04-12。</v>
+        <v>默认延长到最新抽点业务日期 2026-04-13。</v>
       </c>
     </row>
     <row r="4">

--- a/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
+++ b/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>剔除的起始日期后新开店总数</v>
       </c>
       <c r="B4">
-        <v>538</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B6">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>遗留店铺累计回款总额</v>
       </c>
       <c r="B7">
-        <v>81115.47000000002</v>
+        <v>82503.00000000001</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>遗留店铺累计抽点店铺次数</v>
       </c>
       <c r="B8">
-        <v>9245</v>
+        <v>9408</v>
       </c>
     </row>
     <row r="9">
@@ -475,7 +475,7 @@
         <v>导出时间</v>
       </c>
       <c r="B9" t="str">
-        <v>2026/4/14 09:35:14</v>
+        <v>2026/4/15 09:16:41</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1787,27 +1787,56 @@
         <v>2578</v>
       </c>
       <c r="D45">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="E45">
-        <v>316.43</v>
+        <v>1285.06</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>935.32</v>
       </c>
       <c r="H45">
         <v>50</v>
       </c>
       <c r="I45">
-        <v>316.43</v>
+        <v>349.74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B46">
+        <v>559</v>
+      </c>
+      <c r="C46">
+        <v>2578</v>
+      </c>
+      <c r="D46">
+        <v>47</v>
+      </c>
+      <c r="E46">
+        <v>418.9</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>47</v>
+      </c>
+      <c r="I46">
+        <v>418.9</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15576,7 +15605,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G598" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="599">
@@ -21878,7 +21907,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G872" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="873">
@@ -23810,7 +23839,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G956" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="957">
@@ -26156,7 +26185,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1058" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1059">
@@ -26547,7 +26576,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1075" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1076">
@@ -45315,7 +45344,7 @@
         <v>王清月</v>
       </c>
       <c r="G1891" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1892">
@@ -45913,7 +45942,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1917" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1918">
@@ -47638,7 +47667,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1992" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1993">
@@ -49570,7 +49599,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2076" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2077">
@@ -53871,7 +53900,7 @@
         <v>王涛</v>
       </c>
       <c r="G2263" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2264">
@@ -54653,7 +54682,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2297" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2298">
@@ -54676,7 +54705,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2298" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2299">
@@ -56102,7 +56131,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2360" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2361">
@@ -57137,7 +57166,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2405" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2406">
@@ -58724,7 +58753,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2474" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2475">
@@ -59437,7 +59466,7 @@
         <v>王涛</v>
       </c>
       <c r="G2505" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2506">
@@ -60357,7 +60386,7 @@
         <v>王清月</v>
       </c>
       <c r="G2545" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2546">
@@ -61178,7 +61207,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>默认延长到最新抽点业务日期 2026-04-13。</v>
+        <v>默认延长到最新抽点业务日期 2026-04-14。</v>
       </c>
     </row>
     <row r="4">

--- a/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
+++ b/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-15</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>剔除的起始日期后新开店总数</v>
       </c>
       <c r="B4">
-        <v>559</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B6">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>遗留店铺累计回款总额</v>
       </c>
       <c r="B7">
-        <v>82503.00000000001</v>
+        <v>83933.05000000002</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>遗留店铺累计抽点店铺次数</v>
       </c>
       <c r="B8">
-        <v>9408</v>
+        <v>9572</v>
       </c>
     </row>
     <row r="9">
@@ -475,7 +475,7 @@
         <v>导出时间</v>
       </c>
       <c r="B9" t="str">
-        <v>2026/4/15 09:16:41</v>
+        <v>2026/4/16 15:12:27</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1816,27 +1816,56 @@
         <v>2578</v>
       </c>
       <c r="D46">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="E46">
-        <v>418.9</v>
+        <v>1529.73</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>959.63</v>
       </c>
       <c r="H46">
         <v>47</v>
       </c>
       <c r="I46">
-        <v>418.9</v>
+        <v>570.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B47">
+        <v>586</v>
+      </c>
+      <c r="C47">
+        <v>2578</v>
+      </c>
+      <c r="D47">
+        <v>45</v>
+      </c>
+      <c r="E47">
+        <v>319.22</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>45</v>
+      </c>
+      <c r="I47">
+        <v>319.22</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15605,7 +15634,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G598" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="599">
@@ -16111,7 +16140,7 @@
         <v>王郡江</v>
       </c>
       <c r="G620" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="621">
@@ -25886,7 +25915,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1045" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1046">
@@ -45712,7 +45741,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1907" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1908">
@@ -53095,7 +53124,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2228" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2229">
@@ -53831,7 +53860,7 @@
         <v>王清月</v>
       </c>
       <c r="G2260" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2261">
@@ -53900,7 +53929,7 @@
         <v>王涛</v>
       </c>
       <c r="G2263" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2264">
@@ -54682,7 +54711,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2297" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2298">
@@ -57442,7 +57471,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2417" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2418">
@@ -58523,7 +58552,7 @@
         <v>王涛</v>
       </c>
       <c r="G2464" t="str">
-        <v>已解约</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2465">
@@ -58684,7 +58713,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2471" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2472">
@@ -58937,7 +58966,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2482" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2483">
@@ -59213,7 +59242,7 @@
         <v>王涛</v>
       </c>
       <c r="G2494" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2495">
@@ -59742,7 +59771,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2517" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2518">
@@ -61207,7 +61236,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>默认延长到最新抽点业务日期 2026-04-14。</v>
+        <v>默认延长到最新抽点业务日期 2026-04-15。</v>
       </c>
     </row>
     <row r="4">

--- a/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
+++ b/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>剔除的起始日期后新开店总数</v>
       </c>
       <c r="B4">
-        <v>586</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B6">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>遗留店铺累计回款总额</v>
       </c>
       <c r="B7">
-        <v>83933.05000000002</v>
+        <v>85700.87</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>遗留店铺累计抽点店铺次数</v>
       </c>
       <c r="B8">
-        <v>9572</v>
+        <v>9741</v>
       </c>
     </row>
     <row r="9">
@@ -475,7 +475,7 @@
         <v>导出时间</v>
       </c>
       <c r="B9" t="str">
-        <v>2026/4/16 15:12:27</v>
+        <v>2026/4/17 09:26:55</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -543,7 +543,7 @@
         <v>233</v>
       </c>
       <c r="E2">
-        <v>2717.26</v>
+        <v>2725.05</v>
       </c>
       <c r="F2">
         <v>167</v>
@@ -555,7 +555,7 @@
         <v>66</v>
       </c>
       <c r="I2">
-        <v>702.39</v>
+        <v>710.18</v>
       </c>
     </row>
     <row r="3">
@@ -572,7 +572,7 @@
         <v>238</v>
       </c>
       <c r="E3">
-        <v>2032.87</v>
+        <v>2053.55</v>
       </c>
       <c r="F3">
         <v>175</v>
@@ -584,7 +584,7 @@
         <v>63</v>
       </c>
       <c r="I3">
-        <v>485.84</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="4">
@@ -601,7 +601,7 @@
         <v>232</v>
       </c>
       <c r="E4">
-        <v>1904.98</v>
+        <v>1915.55</v>
       </c>
       <c r="F4">
         <v>171</v>
@@ -613,7 +613,7 @@
         <v>61</v>
       </c>
       <c r="I4">
-        <v>461.25</v>
+        <v>471.82</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         <v>240</v>
       </c>
       <c r="E5">
-        <v>2162.58</v>
+        <v>2171.85</v>
       </c>
       <c r="F5">
         <v>173</v>
@@ -642,7 +642,7 @@
         <v>67</v>
       </c>
       <c r="I5">
-        <v>524.4</v>
+        <v>533.67</v>
       </c>
     </row>
     <row r="6">
@@ -659,7 +659,7 @@
         <v>236</v>
       </c>
       <c r="E6">
-        <v>2037.97</v>
+        <v>2048.42</v>
       </c>
       <c r="F6">
         <v>162</v>
@@ -671,7 +671,7 @@
         <v>74</v>
       </c>
       <c r="I6">
-        <v>489.81</v>
+        <v>500.26</v>
       </c>
     </row>
     <row r="7">
@@ -688,7 +688,7 @@
         <v>247</v>
       </c>
       <c r="E7">
-        <v>2118.22</v>
+        <v>2132.55</v>
       </c>
       <c r="F7">
         <v>180</v>
@@ -700,7 +700,7 @@
         <v>67</v>
       </c>
       <c r="I7">
-        <v>607.11</v>
+        <v>621.44</v>
       </c>
     </row>
     <row r="8">
@@ -717,7 +717,7 @@
         <v>253</v>
       </c>
       <c r="E8">
-        <v>2401.95</v>
+        <v>2416.26</v>
       </c>
       <c r="F8">
         <v>182</v>
@@ -729,7 +729,7 @@
         <v>71</v>
       </c>
       <c r="I8">
-        <v>595.13</v>
+        <v>609.44</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +746,7 @@
         <v>248</v>
       </c>
       <c r="E9">
-        <v>2410.25</v>
+        <v>2431.64</v>
       </c>
       <c r="F9">
         <v>174</v>
@@ -758,7 +758,7 @@
         <v>74</v>
       </c>
       <c r="I9">
-        <v>684.74</v>
+        <v>706.13</v>
       </c>
     </row>
     <row r="10">
@@ -775,7 +775,7 @@
         <v>242</v>
       </c>
       <c r="E10">
-        <v>2030.95</v>
+        <v>2038.38</v>
       </c>
       <c r="F10">
         <v>178</v>
@@ -787,7 +787,7 @@
         <v>64</v>
       </c>
       <c r="I10">
-        <v>524.86</v>
+        <v>532.29</v>
       </c>
     </row>
     <row r="11">
@@ -804,7 +804,7 @@
         <v>245</v>
       </c>
       <c r="E11">
-        <v>1963.22</v>
+        <v>1973</v>
       </c>
       <c r="F11">
         <v>173</v>
@@ -816,7 +816,7 @@
         <v>72</v>
       </c>
       <c r="I11">
-        <v>532.08</v>
+        <v>541.86</v>
       </c>
     </row>
     <row r="12">
@@ -833,7 +833,7 @@
         <v>240</v>
       </c>
       <c r="E12">
-        <v>1871.87</v>
+        <v>1883.92</v>
       </c>
       <c r="F12">
         <v>172</v>
@@ -845,7 +845,7 @@
         <v>68</v>
       </c>
       <c r="I12">
-        <v>493.92</v>
+        <v>505.97</v>
       </c>
     </row>
     <row r="13">
@@ -862,7 +862,7 @@
         <v>231</v>
       </c>
       <c r="E13">
-        <v>1955.13</v>
+        <v>1964.99</v>
       </c>
       <c r="F13">
         <v>167</v>
@@ -874,7 +874,7 @@
         <v>64</v>
       </c>
       <c r="I13">
-        <v>494.2</v>
+        <v>504.06</v>
       </c>
     </row>
     <row r="14">
@@ -891,7 +891,7 @@
         <v>242</v>
       </c>
       <c r="E14">
-        <v>2134.61</v>
+        <v>2139.65</v>
       </c>
       <c r="F14">
         <v>173</v>
@@ -903,7 +903,7 @@
         <v>69</v>
       </c>
       <c r="I14">
-        <v>593.3</v>
+        <v>598.34</v>
       </c>
     </row>
     <row r="15">
@@ -920,7 +920,7 @@
         <v>226</v>
       </c>
       <c r="E15">
-        <v>2266.4</v>
+        <v>2273.98</v>
       </c>
       <c r="F15">
         <v>160</v>
@@ -932,7 +932,7 @@
         <v>66</v>
       </c>
       <c r="I15">
-        <v>419.08</v>
+        <v>426.66</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         <v>228</v>
       </c>
       <c r="E16">
-        <v>2246.06</v>
+        <v>2264.01</v>
       </c>
       <c r="F16">
         <v>169</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="I16">
-        <v>488.1</v>
+        <v>506.05</v>
       </c>
     </row>
     <row r="17">
@@ -978,7 +978,7 @@
         <v>217</v>
       </c>
       <c r="E17">
-        <v>1868.88</v>
+        <v>1875</v>
       </c>
       <c r="F17">
         <v>163</v>
@@ -990,7 +990,7 @@
         <v>54</v>
       </c>
       <c r="I17">
-        <v>422.59</v>
+        <v>428.71</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>227</v>
       </c>
       <c r="E18">
-        <v>2089.17</v>
+        <v>2105.03</v>
       </c>
       <c r="F18">
         <v>162</v>
@@ -1019,7 +1019,7 @@
         <v>65</v>
       </c>
       <c r="I18">
-        <v>507.2</v>
+        <v>523.06</v>
       </c>
     </row>
     <row r="19">
@@ -1036,7 +1036,7 @@
         <v>225</v>
       </c>
       <c r="E19">
-        <v>2020.37</v>
+        <v>2032.14</v>
       </c>
       <c r="F19">
         <v>163</v>
@@ -1048,7 +1048,7 @@
         <v>62</v>
       </c>
       <c r="I19">
-        <v>568.33</v>
+        <v>580.1</v>
       </c>
     </row>
     <row r="20">
@@ -1065,7 +1065,7 @@
         <v>226</v>
       </c>
       <c r="E20">
-        <v>1844.77</v>
+        <v>1857.59</v>
       </c>
       <c r="F20">
         <v>162</v>
@@ -1077,7 +1077,7 @@
         <v>64</v>
       </c>
       <c r="I20">
-        <v>433.73</v>
+        <v>446.55</v>
       </c>
     </row>
     <row r="21">
@@ -1094,7 +1094,7 @@
         <v>213</v>
       </c>
       <c r="E21">
-        <v>1932.12</v>
+        <v>1942.58</v>
       </c>
       <c r="F21">
         <v>151</v>
@@ -1106,7 +1106,7 @@
         <v>62</v>
       </c>
       <c r="I21">
-        <v>502.89</v>
+        <v>513.35</v>
       </c>
     </row>
     <row r="22">
@@ -1123,7 +1123,7 @@
         <v>225</v>
       </c>
       <c r="E22">
-        <v>2211.19</v>
+        <v>2226.91</v>
       </c>
       <c r="F22">
         <v>165</v>
@@ -1135,7 +1135,7 @@
         <v>60</v>
       </c>
       <c r="I22">
-        <v>651.88</v>
+        <v>667.6</v>
       </c>
     </row>
     <row r="23">
@@ -1152,7 +1152,7 @@
         <v>215</v>
       </c>
       <c r="E23">
-        <v>1999.79</v>
+        <v>2013.63</v>
       </c>
       <c r="F23">
         <v>152</v>
@@ -1164,7 +1164,7 @@
         <v>63</v>
       </c>
       <c r="I23">
-        <v>497.94</v>
+        <v>511.78</v>
       </c>
     </row>
     <row r="24">
@@ -1181,7 +1181,7 @@
         <v>207</v>
       </c>
       <c r="E24">
-        <v>1922.41</v>
+        <v>1938.34</v>
       </c>
       <c r="F24">
         <v>151</v>
@@ -1193,7 +1193,7 @@
         <v>56</v>
       </c>
       <c r="I24">
-        <v>434.19</v>
+        <v>450.12</v>
       </c>
     </row>
     <row r="25">
@@ -1210,7 +1210,7 @@
         <v>210</v>
       </c>
       <c r="E25">
-        <v>1930.23</v>
+        <v>1935.73</v>
       </c>
       <c r="F25">
         <v>153</v>
@@ -1222,7 +1222,7 @@
         <v>57</v>
       </c>
       <c r="I25">
-        <v>508.57</v>
+        <v>514.07</v>
       </c>
     </row>
     <row r="26">
@@ -1239,7 +1239,7 @@
         <v>211</v>
       </c>
       <c r="E26">
-        <v>1568.9</v>
+        <v>1580.44</v>
       </c>
       <c r="F26">
         <v>157</v>
@@ -1251,7 +1251,7 @@
         <v>54</v>
       </c>
       <c r="I26">
-        <v>357.93</v>
+        <v>369.47</v>
       </c>
     </row>
     <row r="27">
@@ -1268,7 +1268,7 @@
         <v>221</v>
       </c>
       <c r="E27">
-        <v>1719.8</v>
+        <v>1733.54</v>
       </c>
       <c r="F27">
         <v>163</v>
@@ -1280,7 +1280,7 @@
         <v>58</v>
       </c>
       <c r="I27">
-        <v>520.66</v>
+        <v>534.4</v>
       </c>
     </row>
     <row r="28">
@@ -1297,7 +1297,7 @@
         <v>213</v>
       </c>
       <c r="E28">
-        <v>1789.57</v>
+        <v>1800.8</v>
       </c>
       <c r="F28">
         <v>154</v>
@@ -1309,7 +1309,7 @@
         <v>59</v>
       </c>
       <c r="I28">
-        <v>497.23</v>
+        <v>508.46</v>
       </c>
     </row>
     <row r="29">
@@ -1326,7 +1326,7 @@
         <v>224</v>
       </c>
       <c r="E29">
-        <v>2046.83</v>
+        <v>2060.08</v>
       </c>
       <c r="F29">
         <v>157</v>
@@ -1338,7 +1338,7 @@
         <v>67</v>
       </c>
       <c r="I29">
-        <v>520.83</v>
+        <v>534.08</v>
       </c>
     </row>
     <row r="30">
@@ -1355,7 +1355,7 @@
         <v>198</v>
       </c>
       <c r="E30">
-        <v>1807.42</v>
+        <v>1817.18</v>
       </c>
       <c r="F30">
         <v>142</v>
@@ -1367,7 +1367,7 @@
         <v>56</v>
       </c>
       <c r="I30">
-        <v>432.98</v>
+        <v>442.74</v>
       </c>
     </row>
     <row r="31">
@@ -1384,7 +1384,7 @@
         <v>198</v>
       </c>
       <c r="E31">
-        <v>1525.7</v>
+        <v>1538.37</v>
       </c>
       <c r="F31">
         <v>141</v>
@@ -1396,7 +1396,7 @@
         <v>57</v>
       </c>
       <c r="I31">
-        <v>480.11</v>
+        <v>492.78</v>
       </c>
     </row>
     <row r="32">
@@ -1413,7 +1413,7 @@
         <v>190</v>
       </c>
       <c r="E32">
-        <v>1485.52</v>
+        <v>1494.3</v>
       </c>
       <c r="F32">
         <v>135</v>
@@ -1425,7 +1425,7 @@
         <v>55</v>
       </c>
       <c r="I32">
-        <v>417.3</v>
+        <v>426.08</v>
       </c>
     </row>
     <row r="33">
@@ -1442,7 +1442,7 @@
         <v>202</v>
       </c>
       <c r="E33">
-        <v>1552.34</v>
+        <v>1564.09</v>
       </c>
       <c r="F33">
         <v>142</v>
@@ -1454,7 +1454,7 @@
         <v>60</v>
       </c>
       <c r="I33">
-        <v>460.39</v>
+        <v>472.14</v>
       </c>
     </row>
     <row r="34">
@@ -1471,7 +1471,7 @@
         <v>196</v>
       </c>
       <c r="E34">
-        <v>1537.75</v>
+        <v>1552.12</v>
       </c>
       <c r="F34">
         <v>136</v>
@@ -1483,7 +1483,7 @@
         <v>60</v>
       </c>
       <c r="I34">
-        <v>495.35</v>
+        <v>509.72</v>
       </c>
     </row>
     <row r="35">
@@ -1500,7 +1500,7 @@
         <v>188</v>
       </c>
       <c r="E35">
-        <v>1728.46</v>
+        <v>1734.42</v>
       </c>
       <c r="F35">
         <v>133</v>
@@ -1512,7 +1512,7 @@
         <v>55</v>
       </c>
       <c r="I35">
-        <v>522.64</v>
+        <v>528.6</v>
       </c>
     </row>
     <row r="36">
@@ -1587,7 +1587,7 @@
         <v>190</v>
       </c>
       <c r="E38">
-        <v>1563.74</v>
+        <v>1577.62</v>
       </c>
       <c r="F38">
         <v>138</v>
@@ -1599,7 +1599,7 @@
         <v>52</v>
       </c>
       <c r="I38">
-        <v>407.96</v>
+        <v>421.84</v>
       </c>
     </row>
     <row r="39">
@@ -1616,7 +1616,7 @@
         <v>184</v>
       </c>
       <c r="E39">
-        <v>1378.63</v>
+        <v>1386.92</v>
       </c>
       <c r="F39">
         <v>129</v>
@@ -1628,7 +1628,7 @@
         <v>55</v>
       </c>
       <c r="I39">
-        <v>367.48</v>
+        <v>375.77</v>
       </c>
     </row>
     <row r="40">
@@ -1645,7 +1645,7 @@
         <v>173</v>
       </c>
       <c r="E40">
-        <v>1311.44</v>
+        <v>1328.17</v>
       </c>
       <c r="F40">
         <v>121</v>
@@ -1657,7 +1657,7 @@
         <v>52</v>
       </c>
       <c r="I40">
-        <v>343.7</v>
+        <v>360.43</v>
       </c>
     </row>
     <row r="41">
@@ -1845,27 +1845,56 @@
         <v>2578</v>
       </c>
       <c r="D47">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="E47">
-        <v>319.22</v>
+        <v>1341.67</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>936.68</v>
       </c>
       <c r="H47">
         <v>45</v>
       </c>
       <c r="I47">
-        <v>319.22</v>
+        <v>404.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B48">
+        <v>609</v>
+      </c>
+      <c r="C48">
+        <v>2578</v>
+      </c>
+      <c r="D48">
+        <v>50</v>
+      </c>
+      <c r="E48">
+        <v>306.92</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>50</v>
+      </c>
+      <c r="I48">
+        <v>306.92</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13265,7 +13294,7 @@
         <v>王郡江</v>
       </c>
       <c r="G495" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="496">
@@ -28836,7 +28865,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1172" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1173">
@@ -31596,7 +31625,7 @@
         <v>王涛</v>
       </c>
       <c r="G1292" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1293">
@@ -46132,7 +46161,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1924" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1925">
@@ -49283,7 +49312,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2061" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2062">
@@ -49651,7 +49680,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2077" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2078">
@@ -49674,7 +49703,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2078" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2079">
@@ -50939,7 +50968,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2133" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2134">
@@ -54688,7 +54717,7 @@
         <v>王涛</v>
       </c>
       <c r="G2296" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2297">
@@ -54849,7 +54878,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2303" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2304">
@@ -57724,7 +57753,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2428" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2429">
@@ -58874,7 +58903,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2478" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2479">
@@ -60461,7 +60490,7 @@
         <v>王清月</v>
       </c>
       <c r="G2547" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2548">
@@ -61236,7 +61265,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>默认延长到最新抽点业务日期 2026-04-15。</v>
+        <v>默认延长到最新抽点业务日期 2026-04-16。</v>
       </c>
     </row>
     <row r="4">

--- a/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
+++ b/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-19</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>剔除的起始日期后新开店总数</v>
       </c>
       <c r="B4">
-        <v>609</v>
+        <v>637</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B6">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>遗留店铺累计回款总额</v>
       </c>
       <c r="B7">
-        <v>85700.87</v>
+        <v>89940.87</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>遗留店铺累计抽点店铺次数</v>
       </c>
       <c r="B8">
-        <v>9741</v>
+        <v>10223</v>
       </c>
     </row>
     <row r="9">
@@ -475,7 +475,7 @@
         <v>导出时间</v>
       </c>
       <c r="B9" t="str">
-        <v>2026/4/17 09:26:55</v>
+        <v>2026/4/20 10:46:58</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I51"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1848,7 +1848,7 @@
         <v>164</v>
       </c>
       <c r="E47">
-        <v>1341.67</v>
+        <v>1348.05</v>
       </c>
       <c r="F47">
         <v>119</v>
@@ -1860,7 +1860,7 @@
         <v>45</v>
       </c>
       <c r="I47">
-        <v>404.99</v>
+        <v>411.37</v>
       </c>
     </row>
     <row r="48">
@@ -1874,27 +1874,114 @@
         <v>2578</v>
       </c>
       <c r="D48">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="E48">
-        <v>306.92</v>
+        <v>1325.39</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>947.33</v>
       </c>
       <c r="H48">
         <v>50</v>
       </c>
       <c r="I48">
-        <v>306.92</v>
+        <v>378.06</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B49">
+        <v>630</v>
+      </c>
+      <c r="C49">
+        <v>2578</v>
+      </c>
+      <c r="D49">
+        <v>157</v>
+      </c>
+      <c r="E49">
+        <v>1299.29</v>
+      </c>
+      <c r="F49">
+        <v>109</v>
+      </c>
+      <c r="G49">
+        <v>943.92</v>
+      </c>
+      <c r="H49">
+        <v>48</v>
+      </c>
+      <c r="I49">
+        <v>355.37</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="B50">
+        <v>633</v>
+      </c>
+      <c r="C50">
+        <v>2578</v>
+      </c>
+      <c r="D50">
+        <v>158</v>
+      </c>
+      <c r="E50">
+        <v>1423.92</v>
+      </c>
+      <c r="F50">
+        <v>108</v>
+      </c>
+      <c r="G50">
+        <v>988.92</v>
+      </c>
+      <c r="H50">
+        <v>50</v>
+      </c>
+      <c r="I50">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="B51">
+        <v>637</v>
+      </c>
+      <c r="C51">
+        <v>2578</v>
+      </c>
+      <c r="D51">
+        <v>47</v>
+      </c>
+      <c r="E51">
+        <v>491.94</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>47</v>
+      </c>
+      <c r="I51">
+        <v>491.94</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -28796,7 +28883,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1169" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1170">
@@ -28842,7 +28929,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1171" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1172">
@@ -29647,7 +29734,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1206" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1207">
@@ -33580,7 +33667,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1377" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1378">
@@ -33971,7 +34058,7 @@
         <v>王涛</v>
       </c>
       <c r="G1394" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1395">
@@ -34592,7 +34679,7 @@
         <v>王清月</v>
       </c>
       <c r="G1421" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1422">
@@ -39537,7 +39624,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1636" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1637">
@@ -41929,7 +42016,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1740" t="str">
-        <v/>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1741">
@@ -41975,7 +42062,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1742" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1743">
@@ -42504,7 +42591,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1765" t="str">
-        <v/>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1766">
@@ -42527,7 +42614,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1766" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1767">
@@ -44298,7 +44385,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1843" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1844">
@@ -45586,7 +45673,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1899" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1900">
@@ -45954,7 +46041,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1915" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1916">
@@ -46138,7 +46225,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1923" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1924">
@@ -46299,7 +46386,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1930" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1931">
@@ -47932,7 +48019,7 @@
         <v>王清月</v>
       </c>
       <c r="G2001" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2002">
@@ -49059,7 +49146,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2050" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2051">
@@ -49956,7 +50043,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2089" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2090">
@@ -50968,7 +51055,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2133" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2134">
@@ -52693,7 +52780,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2208" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2209">
@@ -53705,7 +53792,7 @@
         <v>王涛</v>
       </c>
       <c r="G2252" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2253">
@@ -55315,7 +55402,7 @@
         <v>王涛</v>
       </c>
       <c r="G2322" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2323">
@@ -55453,7 +55540,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2328" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2329">
@@ -55476,7 +55563,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2329" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2330">
@@ -57224,7 +57311,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2405" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2406">
@@ -57983,7 +58070,7 @@
         <v>王清月</v>
       </c>
       <c r="G2438" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2439">
@@ -58742,7 +58829,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2471" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2472">
@@ -58995,7 +59082,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2482" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2483">
@@ -59800,7 +59887,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2517" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2518">
@@ -61265,7 +61352,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>默认延长到最新抽点业务日期 2026-04-16。</v>
+        <v>默认延长到最新抽点业务日期 2026-04-19。</v>
       </c>
     </row>
     <row r="4">

--- a/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
+++ b/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-22</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>剔除的起始日期后新开店总数</v>
       </c>
       <c r="B4">
-        <v>637</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>遗留店铺累计回款总额</v>
       </c>
       <c r="B7">
-        <v>89940.87</v>
+        <v>93903.06</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>遗留店铺累计抽点店铺次数</v>
       </c>
       <c r="B8">
-        <v>10223</v>
+        <v>10681</v>
       </c>
     </row>
     <row r="9">
@@ -475,7 +475,7 @@
         <v>导出时间</v>
       </c>
       <c r="B9" t="str">
-        <v>2026/4/20 10:46:58</v>
+        <v>2026/4/23 09:45:45</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I54"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1961,27 +1961,114 @@
         <v>2578</v>
       </c>
       <c r="D51">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="E51">
-        <v>491.94</v>
+        <v>1620.02</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>999.23</v>
       </c>
       <c r="H51">
         <v>47</v>
       </c>
       <c r="I51">
-        <v>491.94</v>
+        <v>620.79</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B52">
+        <v>650</v>
+      </c>
+      <c r="C52">
+        <v>2578</v>
+      </c>
+      <c r="D52">
+        <v>156</v>
+      </c>
+      <c r="E52">
+        <v>1168.48</v>
+      </c>
+      <c r="F52">
+        <v>110</v>
+      </c>
+      <c r="G52">
+        <v>857.66</v>
+      </c>
+      <c r="H52">
+        <v>46</v>
+      </c>
+      <c r="I52">
+        <v>310.82</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B53">
+        <v>679</v>
+      </c>
+      <c r="C53">
+        <v>2578</v>
+      </c>
+      <c r="D53">
+        <v>159</v>
+      </c>
+      <c r="E53">
+        <v>1376.8</v>
+      </c>
+      <c r="F53">
+        <v>108</v>
+      </c>
+      <c r="G53">
+        <v>945.99</v>
+      </c>
+      <c r="H53">
+        <v>51</v>
+      </c>
+      <c r="I53">
+        <v>430.81</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B54">
+        <v>694</v>
+      </c>
+      <c r="C54">
+        <v>2578</v>
+      </c>
+      <c r="D54">
+        <v>40</v>
+      </c>
+      <c r="E54">
+        <v>288.83</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>40</v>
+      </c>
+      <c r="I54">
+        <v>288.83</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9701,7 +9788,7 @@
         <v>王郡江</v>
       </c>
       <c r="G335" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="336">
@@ -23984,7 +24071,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G956" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="957">
@@ -26031,7 +26118,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1045" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1046">
@@ -26330,7 +26417,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1058" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1059">
@@ -27733,7 +27820,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1119" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1120">
@@ -27756,7 +27843,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1120" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1121">
@@ -27779,7 +27866,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1121" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1122">
@@ -28952,7 +29039,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1172" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1173">
@@ -29090,7 +29177,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1178" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1179">
@@ -29734,7 +29821,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1206" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1207">
@@ -31712,7 +31799,7 @@
         <v>王涛</v>
       </c>
       <c r="G1292" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1293">
@@ -34035,7 +34122,7 @@
         <v>王清月</v>
       </c>
       <c r="G1393" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1394">
@@ -34058,7 +34145,7 @@
         <v>王涛</v>
       </c>
       <c r="G1394" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1395">
@@ -35714,7 +35801,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1466" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1467">
@@ -38221,7 +38308,7 @@
         <v>王清月</v>
       </c>
       <c r="G1575" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1576">
@@ -38865,7 +38952,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1603" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1604">
@@ -39624,7 +39711,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1636" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1637">
@@ -41303,7 +41390,7 @@
         <v>王清月</v>
       </c>
       <c r="G1709" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1710">
@@ -41671,7 +41758,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1725" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1726">
@@ -41717,7 +41804,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1727" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1728">
@@ -41740,7 +41827,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1728" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1729">
@@ -43902,7 +43989,7 @@
         <v>王清月</v>
       </c>
       <c r="G1822" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1823">
@@ -46386,7 +46473,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1930" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1931">
@@ -46708,7 +46795,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1944" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1945">
@@ -47122,7 +47209,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1962" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1963">
@@ -47651,7 +47738,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1985" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1986">
@@ -50779,7 +50866,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2121" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2122">
@@ -51331,7 +51418,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2145" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2146">
@@ -51837,7 +51924,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2167" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2168">
@@ -53240,7 +53327,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2228" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2229">
@@ -53792,7 +53879,7 @@
         <v>王涛</v>
       </c>
       <c r="G2252" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2253">
@@ -54344,7 +54431,7 @@
         <v>王涛</v>
       </c>
       <c r="G2276" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2277">
@@ -54528,7 +54615,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2284" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2285">
@@ -55540,7 +55627,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2328" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2329">
@@ -56207,7 +56294,7 @@
         <v>王清月</v>
       </c>
       <c r="G2357" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2358">
@@ -56299,7 +56386,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2361" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2362">
@@ -56483,7 +56570,7 @@
         <v>王涛</v>
       </c>
       <c r="G2369" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2370">
@@ -56897,7 +56984,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2387" t="str">
-        <v/>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2388">
@@ -56966,7 +57053,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2390" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2391">
@@ -58070,7 +58157,7 @@
         <v>王清月</v>
       </c>
       <c r="G2438" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2439">
@@ -58737,7 +58824,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2467" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2468">
@@ -58875,7 +58962,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2473" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2474">
@@ -59611,7 +59698,7 @@
         <v>王涛</v>
       </c>
       <c r="G2505" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2506">
@@ -60370,7 +60457,7 @@
         <v>王涛</v>
       </c>
       <c r="G2538" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2539">
@@ -60692,7 +60779,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2552" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2553">
@@ -61313,7 +61400,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2579" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
   </sheetData>
@@ -61352,7 +61439,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>默认延长到最新抽点业务日期 2026-04-19。</v>
+        <v>默认延长到最新抽点业务日期 2026-04-22。</v>
       </c>
     </row>
     <row r="4">

--- a/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
+++ b/去年遗留店铺自2026年3月起每日抽点与回款统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-26</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>剔除的起始日期后新开店总数</v>
       </c>
       <c r="B4">
-        <v>694</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B6">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>遗留店铺累计回款总额</v>
       </c>
       <c r="B7">
-        <v>93903.06</v>
+        <v>98703.45999999999</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>遗留店铺累计抽点店铺次数</v>
       </c>
       <c r="B8">
-        <v>10681</v>
+        <v>11287</v>
       </c>
     </row>
     <row r="9">
@@ -475,7 +475,7 @@
         <v>导出时间</v>
       </c>
       <c r="B9" t="str">
-        <v>2026/4/23 09:45:45</v>
+        <v>2026/4/27 10:19:13</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I58"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -2048,27 +2048,143 @@
         <v>2578</v>
       </c>
       <c r="D54">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="E54">
-        <v>288.83</v>
+        <v>1167.89</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>834.17</v>
       </c>
       <c r="H54">
         <v>40</v>
       </c>
       <c r="I54">
-        <v>288.83</v>
+        <v>333.72</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B55">
+        <v>709</v>
+      </c>
+      <c r="C55">
+        <v>2578</v>
+      </c>
+      <c r="D55">
+        <v>148</v>
+      </c>
+      <c r="E55">
+        <v>1110.33</v>
+      </c>
+      <c r="F55">
+        <v>108</v>
+      </c>
+      <c r="G55">
+        <v>810.76</v>
+      </c>
+      <c r="H55">
+        <v>40</v>
+      </c>
+      <c r="I55">
+        <v>299.57</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B56">
+        <v>736</v>
+      </c>
+      <c r="C56">
+        <v>2578</v>
+      </c>
+      <c r="D56">
+        <v>149</v>
+      </c>
+      <c r="E56">
+        <v>1285.28</v>
+      </c>
+      <c r="F56">
+        <v>102</v>
+      </c>
+      <c r="G56">
+        <v>776.93</v>
+      </c>
+      <c r="H56">
+        <v>47</v>
+      </c>
+      <c r="I56">
+        <v>508.35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B57">
+        <v>758</v>
+      </c>
+      <c r="C57">
+        <v>2578</v>
+      </c>
+      <c r="D57">
+        <v>156</v>
+      </c>
+      <c r="E57">
+        <v>1151.97</v>
+      </c>
+      <c r="F57">
+        <v>107</v>
+      </c>
+      <c r="G57">
+        <v>787.33</v>
+      </c>
+      <c r="H57">
+        <v>49</v>
+      </c>
+      <c r="I57">
+        <v>364.64</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B58">
+        <v>770</v>
+      </c>
+      <c r="C58">
+        <v>2578</v>
+      </c>
+      <c r="D58">
+        <v>46</v>
+      </c>
+      <c r="E58">
+        <v>373.76</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>46</v>
+      </c>
+      <c r="I58">
+        <v>373.76</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I58"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4682,7 +4798,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G113" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="114">
@@ -8063,7 +8179,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G260" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="261">
@@ -18965,7 +19081,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G734" t="str">
-        <v/>
+        <v>已解约</v>
       </c>
     </row>
     <row r="735">
@@ -22070,7 +22186,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G869" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="870">
@@ -22622,7 +22738,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G893" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="894">
@@ -23335,7 +23451,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G924" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="925">
@@ -26118,7 +26234,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1045" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1046">
@@ -27774,7 +27890,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1117" t="str">
-        <v/>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1118">
@@ -28970,7 +29086,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1169" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1170">
@@ -28993,7 +29109,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1170" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1171">
@@ -29016,7 +29132,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1171" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1172">
@@ -30235,7 +30351,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1224" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1225">
@@ -33754,7 +33870,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1377" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1378">
@@ -34122,7 +34238,7 @@
         <v>王清月</v>
       </c>
       <c r="G1393" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1394">
@@ -35663,7 +35779,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1460" t="str">
-        <v/>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1461">
@@ -36514,7 +36630,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1497" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1498">
@@ -37365,7 +37481,7 @@
         <v>王清月</v>
       </c>
       <c r="G1534" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1535">
@@ -39711,7 +39827,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1636" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1637">
@@ -45760,7 +45876,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1899" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1900">
@@ -46128,7 +46244,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1915" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="1916">
@@ -46312,7 +46428,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1923" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1924">
@@ -46795,7 +46911,7 @@
         <v>王郡江</v>
       </c>
       <c r="G1944" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1945">
@@ -46910,7 +47026,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G1949" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="1950">
@@ -47899,7 +48015,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G1992" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="1993">
@@ -48428,7 +48544,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2015" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2016">
@@ -49095,7 +49211,7 @@
         <v>王清月</v>
       </c>
       <c r="G2044" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="2045">
@@ -50866,7 +50982,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2121" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2122">
@@ -51027,7 +51143,7 @@
         <v>王清月</v>
       </c>
       <c r="G2128" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2129">
@@ -51050,7 +51166,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2129" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2130">
@@ -51142,7 +51258,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2133" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2134">
@@ -51418,7 +51534,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2145" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2146">
@@ -51924,7 +52040,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2167" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2168">
@@ -53672,7 +53788,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2243" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2244">
@@ -53879,7 +53995,7 @@
         <v>王涛</v>
       </c>
       <c r="G2252" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2253">
@@ -54063,7 +54179,7 @@
         <v>王清月</v>
       </c>
       <c r="G2260" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2261">
@@ -54937,7 +55053,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2298" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2299">
@@ -55305,7 +55421,7 @@
         <v>王郡江</v>
       </c>
       <c r="G2314" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2315">
@@ -55489,7 +55605,7 @@
         <v>王涛</v>
       </c>
       <c r="G2322" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2323">
@@ -56363,7 +56479,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2360" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2361">
@@ -56547,7 +56663,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2368" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2369">
@@ -57053,7 +57169,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2390" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2391">
@@ -57628,7 +57744,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G2415" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2416">
@@ -58088,7 +58204,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2435" t="str">
-        <v/>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2436">
@@ -59882,7 +59998,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2513" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="2514">
@@ -59974,7 +60090,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2517" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2518">
@@ -61239,7 +61355,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G2572" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="2573">
@@ -61439,7 +61555,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>默认延长到最新抽点业务日期 2026-04-22。</v>
+        <v>默认延长到最新抽点业务日期 2026-04-26。</v>
       </c>
     </row>
     <row r="4">
